--- a/resultados_algoritmos/resumen_descriptivo.xlsx
+++ b/resultados_algoritmos/resumen_descriptivo.xlsx
@@ -481,25 +481,25 @@
         <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1655408210353926</v>
+        <v>0.2729810003074817</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1622290001250803</v>
+        <v>0.272400000540074</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01522256530057942</v>
+        <v>0.01924780380386367</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1349170051980764</v>
+        <v>0.2289000112796202</v>
       </c>
       <c r="H2" t="n">
-        <v>0.232708000112325</v>
+        <v>0.335900011123158</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002317264943304045</v>
+        <v>0.0003704779512720287</v>
       </c>
       <c r="J2" t="n">
-        <v>0.09195656518657012</v>
+        <v>0.07050968302622977</v>
       </c>
     </row>
     <row r="3">
@@ -515,25 +515,25 @@
         <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07274922973010689</v>
+        <v>0.1372599996102508</v>
       </c>
       <c r="E3" t="n">
-        <v>0.07085449760779738</v>
+        <v>0.1339500013273209</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0088692367928166</v>
+        <v>0.01573240140555267</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05849997978657484</v>
+        <v>0.1100000081351027</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1177919912151992</v>
+        <v>0.1981999957934022</v>
       </c>
       <c r="I3" t="n">
-        <v>7.866336128705168e-05</v>
+        <v>0.0002475084539854357</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1219151986312525</v>
+        <v>0.114617524772146</v>
       </c>
     </row>
     <row r="4">
@@ -549,25 +549,25 @@
         <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0647045680670999</v>
+        <v>0.1014040001609828</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06287499854806811</v>
+        <v>0.09869999485090375</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006280875409744634</v>
+        <v>0.008710656640184696</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05891700857318938</v>
+        <v>0.09460000728722662</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1051249855663627</v>
+        <v>0.1371999969705939</v>
       </c>
       <c r="I4" t="n">
-        <v>3.944939591273483e-05</v>
+        <v>7.587553910319373e-05</v>
       </c>
       <c r="J4" t="n">
-        <v>0.09707004617094799</v>
+        <v>0.08590052292174062</v>
       </c>
     </row>
     <row r="5">
@@ -583,25 +583,25 @@
         <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>1.023375431250315</v>
+        <v>1.698840000026394</v>
       </c>
       <c r="E5" t="n">
-        <v>1.023916513076983</v>
+        <v>1.699899999948684</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0518558235419902</v>
+        <v>0.07273575697665398</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9148340031970292</v>
+        <v>1.517800003057346</v>
       </c>
       <c r="H5" t="n">
-        <v>1.241167017724365</v>
+        <v>1.913400003104471</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002689026435218025</v>
+        <v>0.005290490342966868</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05067135868078739</v>
+        <v>0.04281495430736499</v>
       </c>
     </row>
     <row r="6">
@@ -617,25 +617,25 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4372382900328375</v>
+        <v>0.8268449992465321</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4245415038894862</v>
+        <v>0.8218500079237856</v>
       </c>
       <c r="F6" t="n">
-        <v>0.08171393614303485</v>
+        <v>0.06755634654890914</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3755000070668757</v>
+        <v>0.6851000071037561</v>
       </c>
       <c r="H6" t="n">
-        <v>1.19554199045524</v>
+        <v>1.193499992950819</v>
       </c>
       <c r="I6" t="n">
-        <v>0.006677167359987976</v>
+        <v>0.004563859959036308</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1868865056097853</v>
+        <v>0.08170376141897248</v>
       </c>
     </row>
     <row r="7">
@@ -651,25 +651,25 @@
         <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1786537872976623</v>
+        <v>0.2750829995784443</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1729165087454021</v>
+        <v>0.2732499997364357</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03138082388768467</v>
+        <v>0.009046714416341939</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1662079885136336</v>
+        <v>0.2641000028233975</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4736670234706253</v>
+        <v>0.3460000007180497</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0009847561078698808</v>
+        <v>8.184304173084906e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1756516016948457</v>
+        <v>0.03288721742239881</v>
       </c>
     </row>
     <row r="8">
@@ -685,25 +685,25 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>4.690569540834986</v>
+        <v>7.16790599966771</v>
       </c>
       <c r="E8" t="n">
-        <v>4.696812480688095</v>
+        <v>7.174800004577264</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1204403436467952</v>
+        <v>0.2111764565036593</v>
       </c>
       <c r="G8" t="n">
-        <v>4.388958011986688</v>
+        <v>6.667699999525212</v>
       </c>
       <c r="H8" t="n">
-        <v>5.057834001490846</v>
+        <v>7.641499993042089</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01450587637775813</v>
+        <v>0.0445954957814419</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02567712568767399</v>
+        <v>0.02946138753960348</v>
       </c>
     </row>
     <row r="9">
@@ -719,25 +719,25 @@
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>1.940785930491984</v>
+        <v>3.354983000317588</v>
       </c>
       <c r="E9" t="n">
-        <v>1.946250500623137</v>
+        <v>3.35550000454532</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08692375153114086</v>
+        <v>0.151184763246915</v>
       </c>
       <c r="G9" t="n">
-        <v>1.651875005336478</v>
+        <v>2.837199994246475</v>
       </c>
       <c r="H9" t="n">
-        <v>2.144875004887581</v>
+        <v>3.746300004422665</v>
       </c>
       <c r="I9" t="n">
-        <v>0.007555738580247514</v>
+        <v>0.02285683263802575</v>
       </c>
       <c r="J9" t="n">
-        <v>0.04478791306422236</v>
+        <v>0.04506275090890285</v>
       </c>
     </row>
     <row r="10">
@@ -753,25 +753,25 @@
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3770537310629152</v>
+        <v>0.5969109995930921</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3727500152308494</v>
+        <v>0.5935000008321367</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01697718995459088</v>
+        <v>0.02009982110220238</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3587919927667826</v>
+        <v>0.5821999948238954</v>
       </c>
       <c r="H10" t="n">
-        <v>0.499875022796914</v>
+        <v>0.7545999978901818</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0002882249787542615</v>
+        <v>0.0004040028083405402</v>
       </c>
       <c r="J10" t="n">
-        <v>0.04502591688121518</v>
+        <v>0.0336730620074085</v>
       </c>
     </row>
     <row r="11">
@@ -787,25 +787,25 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>21.61344541906146</v>
+        <v>30.79590399967856</v>
       </c>
       <c r="E11" t="n">
-        <v>21.47787499416154</v>
+        <v>30.77855000447016</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5459495206220579</v>
+        <v>0.5902968383634837</v>
       </c>
       <c r="G11" t="n">
-        <v>20.51574998768046</v>
+        <v>28.93240000412334</v>
       </c>
       <c r="H11" t="n">
-        <v>23.67545798188075</v>
+        <v>33.53290000814013</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2980608790674549</v>
+        <v>0.3484503573819248</v>
       </c>
       <c r="J11" t="n">
-        <v>0.02525971727490383</v>
+        <v>0.01916803086441772</v>
       </c>
     </row>
     <row r="12">
@@ -821,25 +821,25 @@
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>8.803667449974455</v>
+        <v>13.72096699968097</v>
       </c>
       <c r="E12" t="n">
-        <v>8.718750003026798</v>
+        <v>13.76069999969332</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5545565430287963</v>
+        <v>0.3585306775826424</v>
       </c>
       <c r="G12" t="n">
-        <v>7.984541007317603</v>
+        <v>12.82730000093579</v>
       </c>
       <c r="H12" t="n">
-        <v>12.98008399317041</v>
+        <v>14.47530000586994</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3075329594160492</v>
+        <v>0.1285442467678687</v>
       </c>
       <c r="J12" t="n">
-        <v>0.06299153689981843</v>
+        <v>0.02613013190622634</v>
       </c>
     </row>
     <row r="13">
@@ -855,25 +855,25 @@
         <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8294829292572103</v>
+        <v>1.303662999998778</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8202084864024073</v>
+        <v>1.286550002987497</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02837762304826023</v>
+        <v>0.09508254402876685</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7903749938122928</v>
+        <v>1.258400006918237</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9687080164439976</v>
+        <v>2.114399991114624</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0008052894898691502</v>
+        <v>0.009040690178982387</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0342112200834223</v>
+        <v>0.07293491034788589</v>
       </c>
     </row>
   </sheetData>

--- a/resultados_algoritmos/resumen_descriptivo.xlsx
+++ b/resultados_algoritmos/resumen_descriptivo.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,11 +462,6 @@
           <t>variance_ms2</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>cv</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -481,25 +476,22 @@
         <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2729810003074817</v>
+        <v>0.1657866488676518</v>
       </c>
       <c r="E2" t="n">
-        <v>0.272400000540074</v>
+        <v>0.1631249906495214</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01924780380386367</v>
+        <v>0.01824228509334398</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2289000112796202</v>
+        <v>0.1322079915553331</v>
       </c>
       <c r="H2" t="n">
-        <v>0.335900011123158</v>
+        <v>0.2589589857961982</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0003704779512720287</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.07050968302622977</v>
+        <v>0.0003327809654268398</v>
       </c>
     </row>
     <row r="3">
@@ -515,25 +507,22 @@
         <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1372599996102508</v>
+        <v>0.07137580832932144</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1339500013273209</v>
+        <v>0.07018748146947473</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01573240140555267</v>
+        <v>0.008418361783228502</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1100000081351027</v>
+        <v>0.0569589901715517</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1981999957934022</v>
+        <v>0.1038339978549629</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0002475084539854357</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.114617524772146</v>
+        <v>7.086881511332216e-05</v>
       </c>
     </row>
     <row r="4">
@@ -549,25 +538,22 @@
         <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1014040001609828</v>
+        <v>0.06460836069891229</v>
       </c>
       <c r="E4" t="n">
-        <v>0.09869999485090375</v>
+        <v>0.06160451448522508</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008710656640184696</v>
+        <v>0.009019213727103003</v>
       </c>
       <c r="G4" t="n">
-        <v>0.09460000728722662</v>
+        <v>0.05891700857318938</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1371999969705939</v>
+        <v>0.1375410065520555</v>
       </c>
       <c r="I4" t="n">
-        <v>7.587553910319373e-05</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.08590052292174062</v>
+        <v>8.134621625516325e-05</v>
       </c>
     </row>
     <row r="5">
@@ -583,25 +569,22 @@
         <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>1.698840000026394</v>
+        <v>1.030764170864131</v>
       </c>
       <c r="E5" t="n">
-        <v>1.699899999948684</v>
+        <v>1.032000480336137</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07273575697665398</v>
+        <v>0.05608057751366878</v>
       </c>
       <c r="G5" t="n">
-        <v>1.517800003057346</v>
+        <v>0.9154170111287385</v>
       </c>
       <c r="H5" t="n">
-        <v>1.913400003104471</v>
+        <v>1.236042007803917</v>
       </c>
       <c r="I5" t="n">
-        <v>0.005290490342966868</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.04281495430736499</v>
+        <v>0.003145031174266612</v>
       </c>
     </row>
     <row r="6">
@@ -617,25 +600,22 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8268449992465321</v>
+        <v>0.4309103798004799</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8218500079237856</v>
+        <v>0.4222704883432016</v>
       </c>
       <c r="F6" t="n">
-        <v>0.06755634654890914</v>
+        <v>0.03744400717447883</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6851000071037561</v>
+        <v>0.3594160079956055</v>
       </c>
       <c r="H6" t="n">
-        <v>1.193499992950819</v>
+        <v>0.5629169754683971</v>
       </c>
       <c r="I6" t="n">
-        <v>0.004563859959036308</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.08170376141897248</v>
+        <v>0.001402053673282422</v>
       </c>
     </row>
     <row r="7">
@@ -651,25 +631,22 @@
         <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2750829995784443</v>
+        <v>0.1752259107888676</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2732499997364357</v>
+        <v>0.1728750066831708</v>
       </c>
       <c r="F7" t="n">
-        <v>0.009046714416341939</v>
+        <v>0.009034221634301915</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2641000028233975</v>
+        <v>0.1664169831201434</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3460000007180497</v>
+        <v>0.220083020394668</v>
       </c>
       <c r="I7" t="n">
-        <v>8.184304173084906e-05</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.03288721742239881</v>
+        <v>8.161716053768876e-05</v>
       </c>
     </row>
     <row r="8">
@@ -685,25 +662,22 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>7.16790599966771</v>
+        <v>4.732015437330119</v>
       </c>
       <c r="E8" t="n">
-        <v>7.174800004577264</v>
+        <v>4.740896009025164</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2111764565036593</v>
+        <v>0.131007962750837</v>
       </c>
       <c r="G8" t="n">
-        <v>6.667699999525212</v>
+        <v>4.413707996718585</v>
       </c>
       <c r="H8" t="n">
-        <v>7.641499993042089</v>
+        <v>4.988625005353242</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0445954957814419</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.02946138753960348</v>
+        <v>0.01716308630412469</v>
       </c>
     </row>
     <row r="9">
@@ -719,25 +693,22 @@
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>3.354983000317588</v>
+        <v>1.995271278719883</v>
       </c>
       <c r="E9" t="n">
-        <v>3.35550000454532</v>
+        <v>1.944916512002237</v>
       </c>
       <c r="F9" t="n">
-        <v>0.151184763246915</v>
+        <v>0.4099461150868465</v>
       </c>
       <c r="G9" t="n">
-        <v>2.837199994246475</v>
+        <v>1.659166009631008</v>
       </c>
       <c r="H9" t="n">
-        <v>3.746300004422665</v>
+        <v>5.809041002066806</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02285683263802575</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.04506275090890285</v>
+        <v>0.168055817274798</v>
       </c>
     </row>
     <row r="10">
@@ -753,25 +724,22 @@
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5969109995930921</v>
+        <v>0.3837125009158626</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5935000008321367</v>
+        <v>0.3737499937415123</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02009982110220238</v>
+        <v>0.06088642789420749</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5821999948238954</v>
+        <v>0.3596250026021153</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7545999978901818</v>
+        <v>0.966791994869709</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0004040028083405402</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.0336730620074085</v>
+        <v>0.003707157101716527</v>
       </c>
     </row>
     <row r="11">
@@ -787,25 +755,22 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>30.79590399967856</v>
+        <v>21.34521586063784</v>
       </c>
       <c r="E11" t="n">
-        <v>30.77855000447016</v>
+        <v>21.31727099185809</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5902968383634837</v>
+        <v>0.2877965700064693</v>
       </c>
       <c r="G11" t="n">
-        <v>28.93240000412334</v>
+        <v>20.41808300418779</v>
       </c>
       <c r="H11" t="n">
-        <v>33.53290000814013</v>
+        <v>21.9754170102533</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3484503573819248</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.01916803086441772</v>
+        <v>0.08282686570748858</v>
       </c>
     </row>
     <row r="12">
@@ -821,25 +786,22 @@
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>13.72096699968097</v>
+        <v>8.672335450246464</v>
       </c>
       <c r="E12" t="n">
-        <v>13.76069999969332</v>
+        <v>8.624666996183805</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3585306775826424</v>
+        <v>0.5387428218696481</v>
       </c>
       <c r="G12" t="n">
-        <v>12.82730000093579</v>
+        <v>7.943584001623094</v>
       </c>
       <c r="H12" t="n">
-        <v>14.47530000586994</v>
+        <v>13.55779200093821</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1285442467678687</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.02613013190622634</v>
+        <v>0.2902438281160713</v>
       </c>
     </row>
     <row r="13">
@@ -855,25 +817,22 @@
         <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>1.303662999998778</v>
+        <v>0.8174987803795375</v>
       </c>
       <c r="E13" t="n">
-        <v>1.286550002987497</v>
+        <v>0.8134579984471202</v>
       </c>
       <c r="F13" t="n">
-        <v>0.09508254402876685</v>
+        <v>0.01658856030922527</v>
       </c>
       <c r="G13" t="n">
-        <v>1.258400006918237</v>
+        <v>0.7866249943617731</v>
       </c>
       <c r="H13" t="n">
-        <v>2.114399991114624</v>
+        <v>0.9040840086527169</v>
       </c>
       <c r="I13" t="n">
-        <v>0.009040690178982387</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.07293491034788589</v>
+        <v>0.0002751803331328038</v>
       </c>
     </row>
   </sheetData>
